--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N86_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N86_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.86352603905112</v>
+        <v>3.227822981345807</v>
       </c>
       <c r="D2" t="n">
-        <v>19.54634806608707</v>
+        <v>3.176281560739149</v>
       </c>
       <c r="E2" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F2" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.324222603497829</v>
+        <v>0.5401861730683972</v>
       </c>
       <c r="D3" t="n">
-        <v>5.083019559753452</v>
+        <v>0.8259906784599359</v>
       </c>
       <c r="E3" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F3" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.21699023823569</v>
+        <v>1.6602609137133</v>
       </c>
       <c r="D4" t="n">
-        <v>11.68397504311743</v>
+        <v>1.898645944506582</v>
       </c>
       <c r="E4" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F4" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.84551867328826</v>
+        <v>2.574896784409342</v>
       </c>
       <c r="D5" t="n">
-        <v>45.18561277575925</v>
+        <v>7.342662076060879</v>
       </c>
       <c r="E5" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F5" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.680783907060196</v>
+        <v>1.410627384897282</v>
       </c>
       <c r="D6" t="n">
-        <v>14.31613827940966</v>
+        <v>2.32637247040407</v>
       </c>
       <c r="E6" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F6" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.88690487075756</v>
+        <v>8.269122041498104</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44769618105248</v>
+        <v>7.872750629421028</v>
       </c>
       <c r="E7" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F7" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.03126438039708</v>
+        <v>5.205080461814525</v>
       </c>
       <c r="D8" t="n">
-        <v>19.24903113882137</v>
+        <v>3.127967560058473</v>
       </c>
       <c r="E8" t="n">
-        <v>15.20263613121486</v>
+        <v>2.470428371322414</v>
       </c>
       <c r="F8" t="n">
-        <v>15.53504276895296</v>
+        <v>2.524444449954856</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
